--- a/doc/first_and_last_words_stories_D.xlsx
+++ b/doc/first_and_last_words_stories_D.xlsx
@@ -1,22 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://liveunibo-my.sharepoint.com/personal/francesca_schiavon10_studio_unibo_it/Documents/Desktop/Eelbrain/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://liveunibo-my.sharepoint.com/personal/francesca_schiavon10_studio_unibo_it/Documents/Desktop/IMT/TESI/linguistic_pipeline_EEG/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_953D47EDC64DAA0F9222AC7A047C392FA77C6576" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51F7A3B0-1EAF-4A1C-9359-07139CB93B97}"/>
+  <xr:revisionPtr revIDLastSave="144" documentId="11_953D47EDC64DAA0F9222AC7A047C392FA77C6576" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05C44626-09CD-4F56-9E71-1652AE0C5A69}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="1700" yWindow="2920" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="GdSyHtw70zU4aKiYuT/hNEQF3qy7tzvu7FwoI7GTQow="/>
     </ext>
@@ -25,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="34">
   <si>
     <t>BEGIN</t>
   </si>
@@ -39,56 +50,101 @@
     <t xml:space="preserve">durata in 100Hz time points </t>
   </si>
   <si>
-    <t>St2_D</t>
-  </si>
-  <si>
-    <t>Un</t>
-  </si>
-  <si>
     <t>camicia</t>
   </si>
   <si>
-    <t>St4_D</t>
-  </si>
-  <si>
-    <t>Era</t>
-  </si>
-  <si>
     <t>mannaggia</t>
   </si>
   <si>
-    <t>St5_D</t>
-  </si>
-  <si>
-    <t>Leo</t>
-  </si>
-  <si>
     <t>cliente</t>
   </si>
   <si>
-    <t>St6_D</t>
-  </si>
-  <si>
     <t>c'</t>
   </si>
   <si>
     <t>felici</t>
   </si>
   <si>
-    <t>St9_D</t>
-  </si>
-  <si>
     <t>questa</t>
   </si>
   <si>
     <t>andare</t>
+  </si>
+  <si>
+    <t>St01_D</t>
+  </si>
+  <si>
+    <t>mondo</t>
+  </si>
+  <si>
+    <t>un</t>
+  </si>
+  <si>
+    <t>St02_D</t>
+  </si>
+  <si>
+    <t>St03_D</t>
+  </si>
+  <si>
+    <t>St04_D</t>
+  </si>
+  <si>
+    <t>St05_D</t>
+  </si>
+  <si>
+    <t>St06_D</t>
+  </si>
+  <si>
+    <t>St07_D</t>
+  </si>
+  <si>
+    <t>St08_D</t>
+  </si>
+  <si>
+    <t>St09_D</t>
+  </si>
+  <si>
+    <t>St10_D</t>
+  </si>
+  <si>
+    <t>Stima durata media parola, storie gruppo D (circa 0.36 ms)</t>
+  </si>
+  <si>
+    <t>una</t>
+  </si>
+  <si>
+    <t>paura</t>
+  </si>
+  <si>
+    <t>era</t>
+  </si>
+  <si>
+    <t>leo</t>
+  </si>
+  <si>
+    <t>l'</t>
+  </si>
+  <si>
+    <t>incantesimo</t>
+  </si>
+  <si>
+    <t>negli</t>
+  </si>
+  <si>
+    <t>ringraziano</t>
+  </si>
+  <si>
+    <t>Filippo</t>
+  </si>
+  <si>
+    <t>cara</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -107,40 +163,32 @@
       <name val="Aptos Narrow"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF1D1C1D"/>
       <name val="Slack-Lato"/>
     </font>
     <font>
+      <b/>
       <sz val="12"/>
-      <color rgb="FF1D1C1D"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="12"/>
-      <color rgb="FF1D1C1D"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8F8F8"/>
-        <bgColor rgb="FFF8F8F8"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -161,12 +209,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -182,6 +232,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -382,7 +436,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G996"/>
+  <dimension ref="A1:J995"/>
   <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="6" width="10.58203125" customWidth="1"/>
@@ -390,210 +444,280 @@
     <col min="8" max="26" width="10.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.5" customHeight="1">
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:10" ht="37" customHeight="1">
+      <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A2" s="1" t="s">
+      <c r="I1" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1">
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2">
+        <v>236817</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2">
+        <f>ROUND(((C3-B2)*100)/44100,0)</f>
+        <v>20064</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15.75" customHeight="1">
+      <c r="C3">
+        <f>9069165+J1</f>
+        <v>9085165</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4">
+        <v>227115</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="1">
+        <f>ROUND(((C5-B4)*100)/44100,0)</f>
+        <v>21609</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="15.75" customHeight="1">
+      <c r="C5">
+        <f>9740808+J1</f>
+        <v>9756808</v>
+      </c>
+      <c r="D5" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="1">
-        <v>21620</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A3" s="1">
+    </row>
+    <row r="6" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6">
+        <v>193599</v>
+      </c>
+      <c r="D6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6">
+        <f>ROUND(((C7-B6)*100)/44100,0)</f>
+        <v>20369</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="15.75" customHeight="1">
+      <c r="C7">
+        <f>9160452+J1</f>
+        <v>9176452</v>
+      </c>
+      <c r="D7" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" s="6"/>
+    </row>
+    <row r="8" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8">
+        <v>190512</v>
+      </c>
+      <c r="D8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8">
+        <f>ROUND(((C9-B8)*100)/44100,0)</f>
+        <v>21112</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="15.75" customHeight="1">
+      <c r="C9">
+        <f>9485028+J1</f>
+        <v>9501028</v>
+      </c>
+      <c r="D9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10">
+        <v>255339</v>
+      </c>
+      <c r="D10" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10">
+        <f>ROUND(((C11-B10)*100)/44100,0)</f>
+        <v>19804</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="15.75" customHeight="1">
+      <c r="C11">
+        <f>8973027+J1</f>
+        <v>8989027</v>
+      </c>
+      <c r="D11" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="3">
-        <v>227115</v>
-      </c>
-      <c r="C3" s="1">
-        <v>234215.1</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A4" s="1">
-        <v>605</v>
-      </c>
-      <c r="B4" s="1">
-        <v>9740808</v>
-      </c>
-      <c r="C4" s="3">
-        <v>9760829.4000000004</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A5" s="1" t="s">
+      <c r="G11" s="1"/>
+    </row>
+    <row r="12" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12">
+        <v>177842</v>
+      </c>
+      <c r="D12" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="1">
-        <v>21150</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A6" s="1">
-        <v>3</v>
-      </c>
-      <c r="B6" s="3">
-        <v>190512</v>
-      </c>
-      <c r="C6" s="1">
-        <v>203212.79999999999</v>
-      </c>
-      <c r="D6" s="1" t="s">
+      <c r="G12">
+        <f>ROUND(((C13-B12)*100)/44100,0)</f>
+        <v>21611</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="15.75" customHeight="1">
+      <c r="C13">
+        <f>9692298+J1</f>
+        <v>9708298</v>
+      </c>
+      <c r="D13" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A7" s="1">
-        <v>541</v>
-      </c>
-      <c r="B7" s="1">
-        <v>9485028</v>
-      </c>
-      <c r="C7" s="3">
-        <v>9516824.0999999996</v>
-      </c>
-      <c r="D7" s="1" t="s">
+      <c r="G13" s="6"/>
+    </row>
+    <row r="14" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A14" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14">
+        <v>221699</v>
+      </c>
+      <c r="D14" t="s">
+        <v>28</v>
+      </c>
+      <c r="G14">
+        <f>ROUND(((C15-B14)*100)/44100,0)</f>
+        <v>20413</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" customHeight="1">
+      <c r="C15">
+        <f>9207639+J1</f>
+        <v>9223639</v>
+      </c>
+      <c r="D15" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A16" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16">
+        <v>215649</v>
+      </c>
+      <c r="D16" t="s">
+        <v>30</v>
+      </c>
+      <c r="G16">
+        <f>ROUND(((C17-B16)*100)/44100,0)</f>
+        <v>20128</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15.75" customHeight="1">
+      <c r="C17">
+        <f>9076221+J1</f>
+        <v>9092221</v>
+      </c>
+      <c r="D17" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A18" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18">
+        <v>203742</v>
+      </c>
+      <c r="D18" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A8" s="1" t="s">
+      <c r="G18">
+        <f>ROUND(((C19-B18)*100)/44100,0)</f>
+        <v>21262</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15.75" customHeight="1">
+      <c r="C19">
+        <f>9564408+J1</f>
+        <v>9580408</v>
+      </c>
+      <c r="D19" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="4">
-        <v>19837</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="3">
-        <v>255339</v>
-      </c>
-      <c r="C9" s="5">
-        <v>267554.7</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="15.75" customHeight="1">
-      <c r="B10" s="1">
-        <v>8973027</v>
-      </c>
-      <c r="C10" s="6">
-        <v>9002618.0999999996</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A11" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A12" s="1">
-        <v>4</v>
-      </c>
-      <c r="B12" s="3">
-        <v>177842</v>
-      </c>
-      <c r="C12" s="1">
-        <v>181118.7</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G12" s="1">
-        <v>21624</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A13" s="1">
-        <v>571</v>
-      </c>
-      <c r="B13" s="1">
-        <v>9692298</v>
-      </c>
-      <c r="C13" s="3">
-        <v>9713069.0999999996</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A14" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G14" s="4">
-        <v>21282</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A15" s="1">
-        <v>5</v>
-      </c>
-      <c r="B15" s="3">
-        <v>203742</v>
-      </c>
-      <c r="C15" s="5">
-        <v>233156.7</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="15.75" customHeight="1">
-      <c r="B16" s="1">
-        <v>9564408</v>
-      </c>
-      <c r="C16" s="3">
-        <v>9588354.3000000007</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" ht="15.75" customHeight="1"/>
-    <row r="18" ht="15.75" customHeight="1"/>
-    <row r="19" ht="15.75" customHeight="1"/>
-    <row r="20" ht="15.75" customHeight="1"/>
-    <row r="21" ht="15.75" customHeight="1"/>
-    <row r="22" ht="15.75" customHeight="1"/>
-    <row r="23" ht="15.75" customHeight="1"/>
-    <row r="24" ht="15.75" customHeight="1"/>
-    <row r="25" ht="15.75" customHeight="1"/>
-    <row r="26" ht="15.75" customHeight="1"/>
-    <row r="27" ht="15.75" customHeight="1"/>
-    <row r="28" ht="15.75" customHeight="1"/>
-    <row r="29" ht="15.75" customHeight="1"/>
-    <row r="30" ht="15.75" customHeight="1"/>
-    <row r="31" ht="15.75" customHeight="1"/>
-    <row r="32" ht="15.75" customHeight="1"/>
+    </row>
+    <row r="20" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A20" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20">
+        <v>170226</v>
+      </c>
+      <c r="D20" t="s">
+        <v>33</v>
+      </c>
+      <c r="G20">
+        <f>ROUND(((C21-B20)*100)/44100,0)</f>
+        <v>20040</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15.75" customHeight="1">
+      <c r="C21">
+        <f>8991990+J1</f>
+        <v>9007990</v>
+      </c>
+      <c r="D21" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15.75" customHeight="1"/>
+    <row r="23" spans="1:7" ht="15.75" customHeight="1"/>
+    <row r="24" spans="1:7" ht="15.75" customHeight="1"/>
+    <row r="25" spans="1:7" ht="15.75" customHeight="1"/>
+    <row r="26" spans="1:7" ht="15.75" customHeight="1"/>
+    <row r="27" spans="1:7" ht="15.75" customHeight="1"/>
+    <row r="28" spans="1:7" ht="15.75" customHeight="1"/>
+    <row r="29" spans="1:7" ht="15.75" customHeight="1"/>
+    <row r="30" spans="1:7" ht="15.75" customHeight="1"/>
+    <row r="31" spans="1:7" ht="15.75" customHeight="1"/>
+    <row r="32" spans="1:7" ht="15.75" customHeight="1"/>
     <row r="33" ht="15.75" customHeight="1"/>
     <row r="34" ht="15.75" customHeight="1"/>
     <row r="35" ht="15.75" customHeight="1"/>
@@ -1557,7 +1681,6 @@
     <row r="993" ht="15.75" customHeight="1"/>
     <row r="994" ht="15.75" customHeight="1"/>
     <row r="995" ht="15.75" customHeight="1"/>
-    <row r="996" ht="15.75" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
